--- a/sheets/대금율보/검수/십이난간.xlsx
+++ b/sheets/대금율보/검수/십이난간.xlsx
@@ -3415,8 +3415,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –И
-南∧)
-‹</t>
+南∧)</t>
         </is>
       </c>
       <c r="M4" s="22"/>
@@ -3440,8 +3439,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –И
-太)
-‹</t>
+太)</t>
         </is>
       </c>
       <c r="S4" s="22"/>
@@ -3450,8 +3448,7 @@
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⌇
-‹</t>
+          <t xml:space="preserve">⌇</t>
         </is>
       </c>
       <c r="C5" s="22"/>
@@ -3459,8 +3456,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –И
-太)
-‹</t>
+太)</t>
         </is>
       </c>
       <c r="E5" s="22"/>
@@ -3468,8 +3464,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –И
-太)
-‹</t>
+太)</t>
         </is>
       </c>
       <c r="G5" s="22"/>
@@ -3485,8 +3480,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –И
-太)
-‹</t>
+太)</t>
         </is>
       </c>
       <c r="K5" s="22"/>
@@ -3510,8 +3504,7 @@
         <is>
           <t xml:space="preserve">–
 –林ㄴ
-仲
-‹</t>
+仲</t>
         </is>
       </c>
       <c r="Q5" s="22"/>
@@ -3544,8 +3537,7 @@
         <is>
           <t xml:space="preserve">潢潢
 –
-–μ
-‹</t>
+–μ</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
@@ -3593,8 +3585,7 @@
         <is>
           <t xml:space="preserve">南
 –林ㄴ
-仲
-‹</t>
+仲</t>
         </is>
       </c>
       <c r="M6" s="22"/>
@@ -3683,8 +3674,7 @@
         <is>
           <t xml:space="preserve">仲⌇
 –И
-太)
-‹</t>
+太)</t>
         </is>
       </c>
       <c r="K7" s="22"/>
@@ -3712,8 +3702,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –林ㄴ
-仲
-‹</t>
+仲</t>
         </is>
       </c>
       <c r="Q7" s="22"/>
@@ -3721,8 +3710,7 @@
         <is>
           <t xml:space="preserve">仲∧⌇
 –И
-太)
-‹</t>
+太)</t>
         </is>
       </c>
       <c r="S7" s="22"/>
@@ -3757,8 +3745,7 @@
         <is>
           <t xml:space="preserve">–И
 太⌇
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="I8" s="22"/>
@@ -3786,8 +3773,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –И
-太)
-‹</t>
+太)</t>
         </is>
       </c>
       <c r="O8" s="22"/>
@@ -3795,8 +3781,7 @@
         <is>
           <t xml:space="preserve">–И
 黃∧⌇
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="Q8" s="22"/>
@@ -3819,8 +3804,7 @@
       <c r="C9" s="22"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲⌇
-‹</t>
+          <t xml:space="preserve">仲⌇</t>
         </is>
       </c>
       <c r="E9" s="22"/>
@@ -3828,8 +3812,7 @@
         <is>
           <t xml:space="preserve">仲
 –И
-太)
-‹</t>
+太)</t>
         </is>
       </c>
       <c r="G9" s="22"/>
@@ -3849,8 +3832,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –И
-太)
-‹</t>
+太)</t>
         </is>
       </c>
       <c r="K9" s="22"/>
@@ -3911,8 +3893,7 @@
         <is>
           <t xml:space="preserve">–И
 黃∧
-–⌇
-‹</t>
+–⌇</t>
         </is>
       </c>
       <c r="I10" s="22"/>

--- a/sheets/대금율보/검수/십이난간.xlsx
+++ b/sheets/대금율보/검수/십이난간.xlsx
@@ -3196,30 +3196,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="15.29" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="15.29" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="15.29" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="15.29" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="90.91" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="180.73" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="180.73" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="S4" s="22"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="180.73" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="180.73" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="180.73" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="S7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="180.73" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="180.73" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="180.73" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="22"/>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="S10" s="22"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="180.73" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -3975,6 +3975,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="67"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="44"/>
 </worksheet>
 </file>